--- a/sample/QuotationFormat.xlsx
+++ b/sample/QuotationFormat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sanat\Desktop\SnapQuote\backend\sample\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/avinash/Desktop/Dbest/quotationv3/sample/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78559B05-7B4E-48E4-92F2-3B7D6F056935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE48E0B-DA3D-6E46-8F31-0FC05F6156E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="21800" windowHeight="13700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1 (2)" sheetId="6" r:id="rId1"/>
@@ -138,7 +138,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2224,7 +2224,7 @@
     <cellStyle name="Normal 2" xfId="29" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
     <cellStyle name="Normal 2 2" xfId="141" xr:uid="{C778E8BC-2E97-4E61-8FB6-8D3D2255578C}"/>
     <cellStyle name="Normal 4" xfId="142" xr:uid="{01B8C518-8EF6-4420-B080-EC6E08284B6C}"/>
-    <cellStyle name="Percent" xfId="280" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="280" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2526,28 +2526,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60D9CD93-8DFA-441F-A763-783A08145EE2}">
-  <dimension ref="A1:P807"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="17.25"/>
+  <dimension ref="A1:P11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="18" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="50.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="50.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="21" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" style="21" customWidth="1"/>
-    <col min="8" max="9" width="13.140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="28"/>
-    <col min="11" max="11" width="10.42578125" style="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="18"/>
-    <col min="13" max="13" width="9.5703125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="11.5703125" style="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="1"/>
-    <col min="16" max="16" width="9.140625" style="20"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="7" max="7" width="10.5" style="21" customWidth="1"/>
+    <col min="8" max="9" width="13.1640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.1640625" style="28"/>
+    <col min="11" max="11" width="10.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.1640625" style="18"/>
+    <col min="13" max="13" width="9.5" style="8" customWidth="1"/>
+    <col min="14" max="14" width="11.5" style="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.1640625" style="1"/>
+    <col min="16" max="16" width="9.1640625" style="20"/>
+    <col min="17" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="21">
+    <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
@@ -2565,7 +2565,7 @@
       <c r="M1" s="7"/>
       <c r="N1" s="14"/>
     </row>
-    <row r="2" spans="1:15" ht="20.100000000000001" customHeight="1">
+    <row r="2" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2582,7 +2582,7 @@
       <c r="H2" s="37"/>
       <c r="I2" s="33"/>
     </row>
-    <row r="3" spans="1:15" ht="24" customHeight="1">
+    <row r="3" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -2597,7 +2597,7 @@
       <c r="H3" s="37"/>
       <c r="I3" s="33"/>
     </row>
-    <row r="4" spans="1:15" ht="19.5" customHeight="1">
+    <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -2614,7 +2614,7 @@
       <c r="H4" s="40"/>
       <c r="I4" s="41"/>
     </row>
-    <row r="5" spans="1:15" ht="20.100000000000001" customHeight="1">
+    <row r="5" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -2629,7 +2629,7 @@
       <c r="H5" s="37"/>
       <c r="I5" s="33"/>
     </row>
-    <row r="6" spans="1:15" ht="20.100000000000001" customHeight="1">
+    <row r="6" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
@@ -2646,11 +2646,11 @@
       <c r="H6" s="37"/>
       <c r="I6" s="33"/>
     </row>
-    <row r="7" spans="1:15" ht="8.25" customHeight="1">
+    <row r="7" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="22"/>
       <c r="I7" s="23"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>14</v>
       </c>
@@ -2663,7 +2663,7 @@
       <c r="H8"/>
       <c r="I8" s="26"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="29" t="s">
         <v>15</v>
       </c>
@@ -2676,11 +2676,11 @@
       <c r="H9" s="30"/>
       <c r="I9" s="31"/>
     </row>
-    <row r="10" spans="1:15" ht="10.5" customHeight="1">
+    <row r="10" spans="1:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="22"/>
       <c r="I10" s="23"/>
     </row>
-    <row r="11" spans="1:15" ht="42" customHeight="1">
+    <row r="11" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>16</v>
       </c>
@@ -2723,350 +2723,6 @@
       </c>
       <c r="O11" s="10"/>
     </row>
-    <row r="12" spans="1:15" ht="18"/>
-    <row r="13" spans="1:15" ht="18"/>
-    <row r="14" spans="1:15" ht="18"/>
-    <row r="15" spans="1:15" ht="18"/>
-    <row r="16" spans="1:15" ht="18"/>
-    <row r="17" ht="18"/>
-    <row r="18" ht="18"/>
-    <row r="19" ht="18"/>
-    <row r="20" ht="18"/>
-    <row r="21" ht="18"/>
-    <row r="22" ht="18"/>
-    <row r="23" ht="18"/>
-    <row r="24" ht="18"/>
-    <row r="25" ht="18"/>
-    <row r="26" ht="18"/>
-    <row r="27" ht="18"/>
-    <row r="28" ht="18"/>
-    <row r="29" ht="18"/>
-    <row r="30" ht="18"/>
-    <row r="31" ht="18"/>
-    <row r="32" ht="18"/>
-    <row r="33" ht="18"/>
-    <row r="34" ht="18"/>
-    <row r="35" ht="18"/>
-    <row r="36" ht="18"/>
-    <row r="37" ht="18"/>
-    <row r="38" ht="18"/>
-    <row r="39" ht="18"/>
-    <row r="40" ht="18"/>
-    <row r="41" ht="18"/>
-    <row r="42" ht="18"/>
-    <row r="43" ht="18"/>
-    <row r="44" ht="18"/>
-    <row r="45" ht="18"/>
-    <row r="46" ht="18"/>
-    <row r="47" ht="18"/>
-    <row r="48" ht="18"/>
-    <row r="49" ht="18"/>
-    <row r="50" ht="18"/>
-    <row r="51" ht="18"/>
-    <row r="52" ht="18"/>
-    <row r="53" ht="18"/>
-    <row r="54" ht="18"/>
-    <row r="55" ht="18"/>
-    <row r="56" ht="18"/>
-    <row r="57" ht="18"/>
-    <row r="58" ht="18"/>
-    <row r="59" ht="18"/>
-    <row r="60" ht="18"/>
-    <row r="61" ht="18"/>
-    <row r="62" ht="18"/>
-    <row r="63" ht="18"/>
-    <row r="64" ht="18"/>
-    <row r="65" ht="18"/>
-    <row r="66" ht="18"/>
-    <row r="67" ht="18"/>
-    <row r="68" ht="18"/>
-    <row r="69" ht="18"/>
-    <row r="70" ht="18"/>
-    <row r="71" ht="18"/>
-    <row r="72" ht="18"/>
-    <row r="73" ht="18"/>
-    <row r="74" ht="18"/>
-    <row r="75" ht="18"/>
-    <row r="76" ht="18"/>
-    <row r="77" ht="18"/>
-    <row r="78" ht="18"/>
-    <row r="79" ht="18"/>
-    <row r="80" ht="18"/>
-    <row r="81" ht="18"/>
-    <row r="82" ht="18"/>
-    <row r="83" ht="18"/>
-    <row r="84" ht="18"/>
-    <row r="85" ht="18"/>
-    <row r="86" ht="18"/>
-    <row r="87" ht="18"/>
-    <row r="88" ht="18"/>
-    <row r="89" ht="18"/>
-    <row r="90" ht="18"/>
-    <row r="91" ht="18"/>
-    <row r="92" ht="18"/>
-    <row r="93" ht="18"/>
-    <row r="94" ht="18"/>
-    <row r="95" ht="18"/>
-    <row r="96" ht="18"/>
-    <row r="97" ht="18"/>
-    <row r="98" ht="18"/>
-    <row r="99" ht="18"/>
-    <row r="100" ht="18"/>
-    <row r="101" ht="18"/>
-    <row r="102" ht="18"/>
-    <row r="103" ht="18"/>
-    <row r="104" ht="18"/>
-    <row r="105" ht="18"/>
-    <row r="106" ht="18"/>
-    <row r="107" ht="18"/>
-    <row r="108" ht="18"/>
-    <row r="109" ht="18"/>
-    <row r="110" ht="18"/>
-    <row r="111" ht="18"/>
-    <row r="112" ht="18"/>
-    <row r="113" ht="18"/>
-    <row r="114" ht="18"/>
-    <row r="115" ht="18"/>
-    <row r="116" ht="18"/>
-    <row r="117" ht="18"/>
-    <row r="118" ht="18"/>
-    <row r="119" ht="18"/>
-    <row r="120" ht="18"/>
-    <row r="121" ht="18"/>
-    <row r="122" ht="18"/>
-    <row r="123" ht="18"/>
-    <row r="124" ht="18"/>
-    <row r="125" ht="18"/>
-    <row r="126" ht="18"/>
-    <row r="127" ht="18"/>
-    <row r="128" ht="18"/>
-    <row r="129" ht="18"/>
-    <row r="130" ht="18"/>
-    <row r="131" ht="18"/>
-    <row r="132" ht="18"/>
-    <row r="133" ht="18"/>
-    <row r="134" ht="18"/>
-    <row r="135" ht="18"/>
-    <row r="136" ht="18"/>
-    <row r="137" ht="18"/>
-    <row r="138" ht="18"/>
-    <row r="139" ht="18"/>
-    <row r="140" ht="18"/>
-    <row r="141" ht="18"/>
-    <row r="142" ht="18"/>
-    <row r="143" ht="18"/>
-    <row r="144" ht="18"/>
-    <row r="145" ht="18"/>
-    <row r="146" ht="18"/>
-    <row r="147" ht="18"/>
-    <row r="148" ht="18"/>
-    <row r="149" ht="18"/>
-    <row r="150" ht="18"/>
-    <row r="151" ht="18"/>
-    <row r="152" ht="18"/>
-    <row r="153" ht="18"/>
-    <row r="154" ht="18"/>
-    <row r="155" ht="18"/>
-    <row r="156" ht="18"/>
-    <row r="157" ht="18"/>
-    <row r="158" ht="18"/>
-    <row r="159" ht="18"/>
-    <row r="160" ht="18"/>
-    <row r="161" ht="18"/>
-    <row r="162" ht="18"/>
-    <row r="163" ht="18"/>
-    <row r="164" ht="18"/>
-    <row r="165" ht="18"/>
-    <row r="166" ht="18"/>
-    <row r="167" ht="18"/>
-    <row r="168" ht="18"/>
-    <row r="169" ht="18"/>
-    <row r="170" ht="18"/>
-    <row r="171" ht="18"/>
-    <row r="172" ht="18"/>
-    <row r="173" ht="18"/>
-    <row r="174" ht="18"/>
-    <row r="175" ht="18"/>
-    <row r="176" ht="18"/>
-    <row r="177" ht="18"/>
-    <row r="178" ht="18"/>
-    <row r="179" ht="18"/>
-    <row r="180" ht="18"/>
-    <row r="181" ht="18"/>
-    <row r="182" ht="18"/>
-    <row r="183" ht="18"/>
-    <row r="184" ht="18"/>
-    <row r="185" ht="18"/>
-    <row r="186" ht="18"/>
-    <row r="187" ht="18"/>
-    <row r="188" ht="18"/>
-    <row r="189" ht="18"/>
-    <row r="190" ht="18"/>
-    <row r="191" ht="18"/>
-    <row r="192" ht="18"/>
-    <row r="193" ht="18"/>
-    <row r="194" ht="18"/>
-    <row r="195" ht="18"/>
-    <row r="196" ht="18"/>
-    <row r="197" ht="18"/>
-    <row r="198" ht="18"/>
-    <row r="199" ht="18"/>
-    <row r="200" ht="18"/>
-    <row r="201" ht="18"/>
-    <row r="202" ht="18"/>
-    <row r="203" ht="18"/>
-    <row r="204" ht="18"/>
-    <row r="205" ht="18"/>
-    <row r="206" ht="18"/>
-    <row r="207" ht="18"/>
-    <row r="208" ht="18"/>
-    <row r="209" ht="18"/>
-    <row r="210" ht="18"/>
-    <row r="211" ht="18"/>
-    <row r="212" ht="18"/>
-    <row r="213" ht="18"/>
-    <row r="214" ht="18"/>
-    <row r="215" ht="18"/>
-    <row r="216" ht="18"/>
-    <row r="217" ht="18"/>
-    <row r="218" ht="18"/>
-    <row r="219" ht="18"/>
-    <row r="220" ht="18"/>
-    <row r="221" ht="18"/>
-    <row r="222" ht="18"/>
-    <row r="223" ht="18"/>
-    <row r="224" ht="18"/>
-    <row r="225" ht="18"/>
-    <row r="226" ht="18"/>
-    <row r="227" ht="18"/>
-    <row r="228" ht="18"/>
-    <row r="229" ht="18"/>
-    <row r="230" ht="18"/>
-    <row r="231" ht="18"/>
-    <row r="232" ht="18"/>
-    <row r="233" ht="18"/>
-    <row r="234" ht="18"/>
-    <row r="235" ht="18"/>
-    <row r="236" ht="18"/>
-    <row r="237" ht="18"/>
-    <row r="238" ht="18"/>
-    <row r="239" ht="18"/>
-    <row r="240" ht="18"/>
-    <row r="241" ht="18"/>
-    <row r="242" ht="18"/>
-    <row r="243" ht="18"/>
-    <row r="244" ht="18"/>
-    <row r="245" ht="18"/>
-    <row r="246" ht="18"/>
-    <row r="247" ht="18"/>
-    <row r="248" ht="18"/>
-    <row r="249" ht="18"/>
-    <row r="250" ht="18"/>
-    <row r="251" ht="18"/>
-    <row r="252" ht="18"/>
-    <row r="253" ht="18"/>
-    <row r="254" ht="18"/>
-    <row r="255" ht="18"/>
-    <row r="256" ht="18"/>
-    <row r="257" ht="18"/>
-    <row r="258" ht="18"/>
-    <row r="259" ht="18"/>
-    <row r="260" ht="18"/>
-    <row r="261" ht="18"/>
-    <row r="262" ht="18"/>
-    <row r="263" ht="18"/>
-    <row r="264" ht="18"/>
-    <row r="265" ht="18"/>
-    <row r="266" ht="18"/>
-    <row r="267" ht="18"/>
-    <row r="268" ht="18"/>
-    <row r="269" ht="18"/>
-    <row r="270" ht="18"/>
-    <row r="271" ht="18"/>
-    <row r="272" ht="18"/>
-    <row r="273" ht="18"/>
-    <row r="274" ht="18"/>
-    <row r="275" ht="18"/>
-    <row r="276" ht="18"/>
-    <row r="277" ht="18"/>
-    <row r="278" ht="18"/>
-    <row r="279" ht="18"/>
-    <row r="280" ht="18"/>
-    <row r="281" ht="18"/>
-    <row r="282" ht="18"/>
-    <row r="283" ht="18"/>
-    <row r="284" ht="18"/>
-    <row r="285" ht="18"/>
-    <row r="286" ht="18"/>
-    <row r="287" ht="18"/>
-    <row r="288" ht="18"/>
-    <row r="289" ht="18"/>
-    <row r="290" ht="18"/>
-    <row r="291" ht="18"/>
-    <row r="292" ht="18"/>
-    <row r="293" ht="18"/>
-    <row r="294" ht="18"/>
-    <row r="295" ht="18"/>
-    <row r="296" ht="18"/>
-    <row r="297" ht="18"/>
-    <row r="298" ht="18"/>
-    <row r="299" ht="18"/>
-    <row r="300" ht="18"/>
-    <row r="301" ht="18"/>
-    <row r="302" ht="18"/>
-    <row r="303" ht="18"/>
-    <row r="304" ht="18"/>
-    <row r="305" ht="18"/>
-    <row r="306" ht="18"/>
-    <row r="307" ht="18"/>
-    <row r="308" ht="18"/>
-    <row r="309" ht="18"/>
-    <row r="310" ht="18"/>
-    <row r="311" ht="18"/>
-    <row r="312" ht="18"/>
-    <row r="313" ht="18"/>
-    <row r="314" ht="18"/>
-    <row r="315" ht="18"/>
-    <row r="316" ht="18"/>
-    <row r="317" ht="18"/>
-    <row r="318" ht="18"/>
-    <row r="319" ht="18"/>
-    <row r="320" ht="18"/>
-    <row r="321" ht="18"/>
-    <row r="322" ht="18"/>
-    <row r="323" ht="18"/>
-    <row r="324" ht="18"/>
-    <row r="325" ht="18"/>
-    <row r="326" ht="18"/>
-    <row r="327" ht="18"/>
-    <row r="328" ht="18"/>
-    <row r="329" ht="18"/>
-    <row r="330" ht="18"/>
-    <row r="331" ht="18"/>
-    <row r="332" ht="18"/>
-    <row r="333" ht="18"/>
-    <row r="334" ht="18"/>
-    <row r="335" ht="18"/>
-    <row r="336" ht="18"/>
-    <row r="337" ht="18"/>
-    <row r="338" ht="18"/>
-    <row r="339" ht="18"/>
-    <row r="340" ht="18"/>
-    <row r="341" ht="18"/>
-    <row r="342" ht="18"/>
-    <row r="343" ht="18"/>
-    <row r="344" ht="18"/>
-    <row r="345" ht="18"/>
-    <row r="346" ht="18"/>
-    <row r="347" ht="18"/>
-    <row r="348" ht="18"/>
-    <row r="349" ht="18"/>
-    <row r="350" ht="18"/>
-    <row r="351" ht="18"/>
-    <row r="690" ht="18"/>
-    <row r="729" ht="18"/>
-    <row r="768" ht="18"/>
-    <row r="807" ht="18"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A9:I9"/>
@@ -3085,7 +2741,7 @@
   <phoneticPr fontId="9" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.9" bottom="0.88" header="0.118110236220472" footer="0.118110236220472"/>
-  <pageSetup paperSize="9" scale="80" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="74" orientation="landscape" r:id="rId1"/>
   <headerFooter scaleWithDoc="0">
     <oddHeader>&amp;C&amp;"Arial Black,Bold"&amp;20&amp;G</oddHeader>
     <oddFooter>&amp;C&amp;G&amp;RPage &amp;P of &amp;N</oddFooter>

--- a/sample/QuotationFormat.xlsx
+++ b/sample/QuotationFormat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/avinash/Desktop/Dbest/quotationv3/sample/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/avinash/Desktop/Dbest copy 3/quotationv3/sample/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE48E0B-DA3D-6E46-8F31-0FC05F6156E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8D8B41-7CED-1E45-AF60-4D81C07E0627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="21800" windowHeight="13700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>QUOTATION</t>
   </si>
@@ -128,6 +128,9 @@
   </si>
   <si>
     <t>SP</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -2226,7 +2229,18 @@
     <cellStyle name="Normal 4" xfId="142" xr:uid="{01B8C518-8EF6-4420-B080-EC6E08284B6C}"/>
     <cellStyle name="Per cent" xfId="280" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2640,7 +2654,9 @@
       <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="38"/>
+      <c r="E6" s="38" t="s">
+        <v>29</v>
+      </c>
       <c r="F6" s="37"/>
       <c r="G6" s="37"/>
       <c r="H6" s="37"/>
@@ -2740,7 +2756,7 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0" right="0" top="0.9" bottom="0.88" header="0.118110236220472" footer="0.118110236220472"/>
+  <pageMargins left="0" right="0" top="1.05" bottom="0.88" header="0" footer="0.118110236220472"/>
   <pageSetup paperSize="9" scale="74" orientation="landscape" r:id="rId1"/>
   <headerFooter scaleWithDoc="0">
     <oddHeader>&amp;C&amp;"Arial Black,Bold"&amp;20&amp;G</oddHeader>
